--- a/data/ERGA_UNIFIED_DATA.xlsx
+++ b/data/ERGA_UNIFIED_DATA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CK- Laptop\Downloads\rail-main\rail-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F614CDB8-2A2A-4AEA-B700-4F4D2534FDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E9329E-D64A-4E5D-A81E-E2A4AC264568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4164,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="38">
-        <v>46240</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="18" customHeight="1" x14ac:dyDescent="0.3">

--- a/data/ERGA_UNIFIED_DATA.xlsx
+++ b/data/ERGA_UNIFIED_DATA.xlsx
@@ -157,7 +157,7 @@
     <t>Γεωγρ. Μήκος</t>
   </si>
   <si>
-    <t>ΕΠ ΥΜΕΠΕΡΑΑ</t>
+    <t>ΕΠ-ΥΜΕΠΕΡΑΑ (Ημιτελείς πράξεις)</t>
   </si>
   <si>
     <t>ΔΙΑΚΟΠΤΟ-ΡΟΔΟΔΑΦΝΗ</t>
@@ -173,7 +173,7 @@
 </t>
   </si>
   <si>
-    <t>ΕΠ ΥΜΕΠΕΡΑΑ 2014-2020</t>
+    <t>ΕΠ-ΥΜΕΠΕΡΑΑ 2014-2020 (Ημιτελείς πράξεις)</t>
   </si>
   <si>
     <t>39.302.718,72 € (Συγχρηματοδοτούμενη Δημόσια δαπάνη)</t>
